--- a/artfynd/A 62797-2019 artfynd.xlsx
+++ b/artfynd/A 62797-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62797-2019 artfynd.xlsx
+++ b/artfynd/A 62797-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1131,237 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114935760</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57186</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>569287</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6377083</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114935625</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90440</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grönhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>569299</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6377078</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62797-2019 artfynd.xlsx
+++ b/artfynd/A 62797-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1362,6 +1362,497 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114944054</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90447</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>569293</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6377084</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fanns på en grov granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114944110</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99805</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>569293</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6377084</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikliga bestånd</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114944159</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>569288</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6377092</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114944137</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57186</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grönhagen, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>569288</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6377092</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
